--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260731.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ETN US</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>伊頓公開有限公司</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>32,396</t>
+          <t>78,307</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>10.88%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ETN US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>伊頓公開有限公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>78,307</t>
+          <t>32,396</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.24%</t>
+          <t>10.74%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>7.94%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.94%</t>
+          <t>7.30%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.68%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>4.36%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.56%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>51,210</t>
+          <t>49,736</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>49,736</t>
+          <t>51,210</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1056,161 +1056,161 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>11,337</t>
+          <t>32,510</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>32,510</t>
+          <t>47,027</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>47,027</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>30,445</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>30,445</t>
+          <t>95,063</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>95,063</t>
+          <t>27,569</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>27,569</t>
+          <t>11,337</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1276,46 +1276,46 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>145,945</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>30,314</t>
+          <t>145,945</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,39 +1327,39 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>30,314</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1562,24 +1562,24 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,878</t>
+          <t>3,651</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,651</t>
+          <t>5,878</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>100,041,312</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
